--- a/data/trans_dic/P34B04_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,64</t>
+          <t>0,98; 2,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,34</t>
+          <t>1,24; 3,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,47</t>
+          <t>0,97; 3,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,19</t>
+          <t>0,31; 1,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,41</t>
+          <t>0,54; 1,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,56</t>
+          <t>0,56; 1,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,82</t>
+          <t>0,68; 1,9</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 10,84</t>
+          <t>8,18; 10,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,41</t>
+          <t>6,19; 8,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 10,7</t>
+          <t>6,05; 10,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,36</t>
+          <t>0,45; 1,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,1</t>
+          <t>1,09; 2,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,54</t>
+          <t>1,14; 2,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,16</t>
+          <t>4,7; 6,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,17</t>
+          <t>3,89; 5,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,47</t>
+          <t>4,1; 6,48</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 13,98</t>
+          <t>8,07; 13,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,03</t>
+          <t>6,22; 11,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 15,64</t>
+          <t>9,71; 15,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,65</t>
+          <t>1,06; 4,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,74</t>
+          <t>1,25; 3,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,7</t>
+          <t>1,6; 3,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,36</t>
+          <t>4,98; 8,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,83</t>
+          <t>4,25; 7,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 8,9</t>
+          <t>5,85; 9,01</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,42</t>
+          <t>6,53; 8,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,13</t>
+          <t>5,5; 7,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,77</t>
+          <t>6,54; 9,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,13</t>
+          <t>0,5; 1,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,64</t>
+          <t>0,96; 1,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,18</t>
+          <t>1,24; 2,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 4,57</t>
+          <t>3,58; 4,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,2</t>
+          <t>3,3; 4,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 5,66</t>
+          <t>4,11; 5,77</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10750; 25652</t>
+          <t>9559; 26007</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8593; 25219</t>
+          <t>9333; 24639</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4538; 17871</t>
+          <t>5004; 18968</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 11401</t>
+          <t>0; 8921</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6896</t>
+          <t>0; 6845</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2091; 8964</t>
+          <t>2361; 9387</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13048; 32642</t>
+          <t>12426; 29749</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9655; 27370</t>
+          <t>9784; 27712</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8948; 23114</t>
+          <t>8606; 24042</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>159281; 212867</t>
+          <t>160560; 213878</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128817; 174614</t>
+          <t>128460; 179322</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>137001; 244934</t>
+          <t>138396; 246703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8720; 23885</t>
+          <t>7980; 23220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21501; 41769</t>
+          <t>21576; 42395</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25449; 56761</t>
+          <t>25584; 54546</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>173353; 229089</t>
+          <t>174668; 227976</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>159625; 210217</t>
+          <t>158212; 211067</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>187356; 292605</t>
+          <t>185596; 293034</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38602; 67288</t>
+          <t>38840; 67032</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34246; 60348</t>
+          <t>34024; 61607</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62305; 101155</t>
+          <t>62810; 99873</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4748; 21324</t>
+          <t>4855; 19979</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6220; 20550</t>
+          <t>6890; 20388</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10453; 24393</t>
+          <t>10566; 24508</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45818; 78524</t>
+          <t>46822; 78932</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43815; 74851</t>
+          <t>46596; 77628</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76963; 116239</t>
+          <t>76457; 117633</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>223956; 287930</t>
+          <t>223145; 287957</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>186410; 240805</t>
+          <t>185773; 244113</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>222292; 337298</t>
+          <t>225708; 336551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18418; 40188</t>
+          <t>17732; 42385</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32311; 57954</t>
+          <t>33816; 59635</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44902; 79388</t>
+          <t>45284; 78998</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>250759; 318582</t>
+          <t>249232; 317571</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>228818; 290457</t>
+          <t>227973; 293735</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>294875; 401505</t>
+          <t>291601; 409698</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B04_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,67</t>
+          <t>1,03; 2,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,27</t>
+          <t>1,08; 3,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,68</t>
+          <t>1,4; 5,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,25</t>
+          <t>0,3; 1,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,29</t>
+          <t>0,52; 1,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,58</t>
+          <t>0,57; 1,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,9</t>
+          <t>0,94; 2,84</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,18; 10,89</t>
+          <t>8,21; 10,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,64</t>
+          <t>6,19; 8,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,78</t>
+          <t>7,82; 10,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,32</t>
+          <t>0,49; 1,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,13</t>
+          <t>1,08; 2,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,44</t>
+          <t>1,47; 2,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 6,13</t>
+          <t>4,64; 6,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,19</t>
+          <t>3,89; 5,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,48</t>
+          <t>4,82; 6,69</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 13,93</t>
+          <t>8,13; 14,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 11,27</t>
+          <t>6,35; 11,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 15,45</t>
+          <t>10,09; 15,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,36</t>
+          <t>1,02; 4,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,71</t>
+          <t>1,25; 3,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,72</t>
+          <t>1,56; 3,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,4</t>
+          <t>5,04; 8,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,08</t>
+          <t>4,04; 6,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,01</t>
+          <t>6,07; 9,22</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,43</t>
+          <t>6,56; 8,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,23</t>
+          <t>5,54; 7,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 9,75</t>
+          <t>7,66; 10,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,19</t>
+          <t>0,53; 1,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,69</t>
+          <t>0,94; 1,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,17</t>
+          <t>1,43; 2,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,56</t>
+          <t>3,6; 4,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,25</t>
+          <t>3,3; 4,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,77</t>
+          <t>4,65; 6,01</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>21546</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9559; 26007</t>
+          <t>10003; 26298</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9333; 24639</t>
+          <t>8173; 23925</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5004; 18968</t>
+          <t>8086; 33559</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8921</t>
+          <t>0; 9369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6845</t>
+          <t>0; 6902</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2361; 9387</t>
+          <t>2481; 10568</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12426; 29749</t>
+          <t>12126; 30394</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9784; 27712</t>
+          <t>10053; 26880</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8606; 24042</t>
+          <t>13116; 39771</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198085</t>
+          <t>206754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>45536</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>237044</t>
+          <t>252290</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>160560; 213878</t>
+          <t>161223; 214455</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128460; 179322</t>
+          <t>128522; 177467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>138396; 246703</t>
+          <t>174418; 243430</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7980; 23220</t>
+          <t>8685; 22976</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21576; 42395</t>
+          <t>21413; 43003</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25584; 54546</t>
+          <t>31985; 62262</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>174668; 227976</t>
+          <t>172724; 231378</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>158212; 211067</t>
+          <t>158197; 210321</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>185596; 293034</t>
+          <t>212077; 294367</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79430</t>
+          <t>90891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95901</t>
+          <t>108046</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38840; 67032</t>
+          <t>39108; 67898</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34024; 61607</t>
+          <t>34741; 62455</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62810; 99873</t>
+          <t>71799; 112216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4855; 19979</t>
+          <t>4662; 19692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6890; 20388</t>
+          <t>6878; 21528</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10566; 24508</t>
+          <t>11424; 25571</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46822; 78932</t>
+          <t>47374; 78939</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46596; 77628</t>
+          <t>44306; 74290</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76457; 117633</t>
+          <t>87771; 133196</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287239</t>
+          <t>313954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>347502</t>
+          <t>381881</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>223145; 287957</t>
+          <t>224354; 291177</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>185773; 244113</t>
+          <t>187116; 244503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>225708; 336551</t>
+          <t>269444; 359967</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17732; 42385</t>
+          <t>18737; 41292</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33816; 59635</t>
+          <t>33330; 58285</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45284; 78998</t>
+          <t>53293; 87203</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>249232; 317571</t>
+          <t>251093; 316677</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>227973; 293735</t>
+          <t>227964; 290999</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>291601; 409698</t>
+          <t>336750; 435396</t>
         </is>
       </c>
     </row>
